--- a/Projetos_sanear.xlsx
+++ b/Projetos_sanear.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Desktop\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00C3044B-8A0E-4C1E-BFBF-0646FD7830BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8620CAE4-DFE8-4270-9870-901A70AC57F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{572B0F12-F633-4277-80B6-1F2893C03522}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t>PROJETO</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>Cyra</t>
+  </si>
+  <si>
+    <t>Analise de Projeto - Padre Miguel - Construtora Farias</t>
+  </si>
+  <si>
+    <t>Elimary</t>
   </si>
 </sst>
 </file>
@@ -428,10 +434,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDEDB345-BBA8-43D9-A274-BA787E8443AC}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="32.44140625" customWidth="1"/>
+    <col min="1" max="1" width="45.44140625" customWidth="1"/>
+    <col min="2" max="2" width="32.44140625" customWidth="1"/>
     <col min="3" max="3" width="14.21875" customWidth="1"/>
     <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
@@ -509,6 +516,9 @@
       <c r="E4" s="1">
         <v>46226</v>
       </c>
+      <c r="F4" s="1">
+        <v>46226</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -526,6 +536,9 @@
       <c r="E5" s="1">
         <v>46226</v>
       </c>
+      <c r="F5" s="1">
+        <v>46226</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -543,6 +556,9 @@
       <c r="E6" s="1">
         <v>46226</v>
       </c>
+      <c r="F6" s="1">
+        <v>46226</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -592,7 +608,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1">
-        <v>46159</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -610,6 +626,23 @@
       </c>
       <c r="E10" s="1">
         <v>46251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46321</v>
+      </c>
+      <c r="E11" s="1">
+        <v>46382</v>
       </c>
     </row>
   </sheetData>
